--- a/data/activity.xlsx
+++ b/data/activity.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:K189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2958,6 +2958,7286 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-07-14 12:20:53</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Customer Test Customer 1 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-07-14 12:20:59</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>91000002</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>91000002</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Sousse</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Customer Test Customer 2 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-07-14 12:21:04</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>91000003</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>91000003</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Customer Test Customer 3 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-07-14 12:23:04</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>TRX-100028</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Transfer 91000020 → 91000021</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-07-14 12:23:20</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Customer Test Customer 1 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-07-14 12:23:26</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>91000002</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>91000002</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Sousse</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Customer Test Customer 2 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-07-14 12:25:59</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Customer Test Customer 1 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-07-14 12:26:11</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Customer Test Customer 1 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-07-14 12:26:45</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Customer Test Customer 1 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-07-14 12:26:51</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>91000002</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>91000002</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Sousse</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Customer Test Customer 2 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-07-14 12:26:56</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>91000003</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>91000003</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Customer Test Customer 3 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-07-14 12:28:47</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Customer Test Customer 1 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-07-14 12:31:03</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>TRX-100029</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Transfer 91000020 → 91000021</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-07-14 12:35:47</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Customer Test Customer 1 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-07-14 12:37:01</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Customer Test Customer 1 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-07-14 12:37:11</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Customer Test Customer 1 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-07-14 12:42:54</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Customer Test Customer 1 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-07-14 12:43:01</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>91000002</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>91000002</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Sousse</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Customer Test Customer 2 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-07-14 12:43:06</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>91000003</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>91000003</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Customer Test Customer 3 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-07-14 12:43:55</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>TRX-100030</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>91000009</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>91000010</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>100</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Transfer 91000009 → 91000010</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-07-14 12:44:29</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>TRX-100031</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Transfer 91000020 → 91000021</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-07-14 12:45:35</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Sfax</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Customer neyrouz created</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-07-14 14:28:03</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Customer Test Customer 1 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-07-14 14:28:10</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>91000002</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>91000002</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Sousse</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Customer Test Customer 2 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-07-14 14:28:16</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>91000003</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>91000003</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Customer Test Customer 3 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-07-14 14:29:12</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>TRX-100032</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>91000009</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>91000010</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>100</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Transfer 91000009 → 91000010</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-07-14 14:29:48</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>TRX-100033</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Transfer 91000020 → 91000021</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-07-14 14:30:16</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Sfax</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Customer neyrouz created</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-07-14 14:30:33</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>45678945</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>45678945</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Sfax</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Customer maryem created</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-07-14 14:31:45</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>TRX-100034</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>45678945</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>20</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Sfax</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Web Banking</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Transfer 12345678 → 45678945</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-07-14 15:03:12</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Customer Test Customer 1 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-07-14 15:03:18</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>91000002</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>91000002</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Sousse</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Customer Test Customer 2 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-07-14 15:03:24</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>91000003</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>91000003</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Customer Test Customer 3 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-07-14 15:04:10</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>TRX-100035</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>91000009</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>91000010</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>100</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Transfer 91000009 → 91000010</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-07-14 15:04:43</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>TRX-100036</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Transfer 91000020 → 91000021</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-07-14 15:13:29</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Customer Amine Ben Salah created</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-07-14 15:13:34</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>91000002</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>91000002</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Sousse</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Customer Sara Trabelsi created</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-07-14 15:13:39</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>91000003</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>91000003</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Customer Karim Mokhtar created</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-07-14 15:14:25</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>TRX-100037</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>91000009</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>91000010</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>100</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Transfer 91000009 → 91000010</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-07-14 15:14:58</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>TRX-100038</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Transfer 91000020 → 91000021</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-07-14 15:16:38</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Customer Amine Ben Salah created</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-07-14 15:16:44</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>91000002</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>91000002</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Sousse</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Customer Sara Trabelsi created</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-07-14 15:16:49</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>91000003</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>91000003</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Customer Karim Mokhtar created</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-07-14 15:17:38</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>TRX-100039</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>91000009</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>91000010</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>100</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Transfer 91000009 → 91000010</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-07-14 15:18:13</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>TRX-100040</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Transfer 91000020 → 91000021</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:37:30</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Customer Amine Ben Salah created</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:45:54</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>TRX-100041</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>91000009</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>91000010</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>100</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Transfer 91000009 → 91000010</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:46:28</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>TRX-100042</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Transfer 91000020 → 91000021</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:50:16</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Sfax</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Customer amira moussa created</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:50:21</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>91000003</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>91000003</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Customer Generated Customer 3 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:51:12</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>TRX-100043</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>91000009</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>91000010</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>100</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Transfer 91000009 → 91000010</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:51:47</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>TRX-100044</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Transfer 91000020 → 91000021</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:54:12</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>45678945</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>45678945</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Sfax</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Customer Amine  Salah45678978 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:54:18</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Sfax</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Customer amira moussa created</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:54:23</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>91000003</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>91000003</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Customer Generated Customer 3 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:55:13</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>TRX-100045</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>91000009</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>91000010</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>100</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Transfer 91000009 → 91000010</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-07-14 16:55:48</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>TRX-100046</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Transfer 91000020 → 91000021</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:09:24</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>45678945</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>45678945</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Sfax</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Customer Amine  Salah45678978 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:09:30</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Sfax</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Customer amira moussa created</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:12:20</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>45678945</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>45678945</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Sfax</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Customer Amine  Salah45678978 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:12:25</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Sfax</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Customer amira moussa created</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:12:31</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>91000003</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>91000003</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Customer Test Customer 3 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:13:17</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>TRX-100047</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>91000009</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>91000010</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>100</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Transfer 91000009 → 91000010</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:13:50</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>TRX-100048</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Transfer 91000020 → 91000021</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:14:18</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>12457812</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>12457812</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Customer neyrouz created</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:16:56</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Sfax</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Customer amira moussa created</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:17:01</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>91000003</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>91000003</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Customer Test Customer 3 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:17:47</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>TRX-100049</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>91000009</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>91000010</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>100</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Transfer 91000009 → 91000010</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:18:20</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>TRX-100050</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Transfer 91000020 → 91000021</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:20:08</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>45678945</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>45678945</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Sfax</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Customer Amine  Salah45678978 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:20:14</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>12345678</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Sfax</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Customer amira moussa created</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:20:20</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>91000003</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>91000003</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Customer Test Customer 3 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:21:32</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>TRX-100051</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>91000009</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>91000010</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>100</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Transfer 91000009 → 91000010</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:22:10</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>TRX-100052</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Transfer 91000020 → 91000021</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:24:53</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Customer Amine Ben Salah created</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:24:58</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>91000002</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>91000002</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Sousse</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Customer Sara Trabelsi created</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:25:02</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>91000003</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>91000003</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Customer Karim Mokhtar created</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:25:46</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>TRX-100053</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>91000009</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>91000010</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>100</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Transfer 91000009 → 91000010</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:26:18</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>TRX-100054</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Transfer 91000020 → 91000021</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:32:35</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Customer Amine Ben Salah created</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:32:41</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>91000002</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>91000002</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Sousse</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Customer Sara Trabelsi created</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:32:46</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>91000003</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>91000003</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>0</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Customer Karim Mokhtar created</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:33:34</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>TRX-100055</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>91000009</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>91000010</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>100</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Transfer 91000009 → 91000010</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:34:10</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>TRX-100056</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Transfer 91000020 → 91000021</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:34:48</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>91000002</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>91000002</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Sousse</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Customer Sara Trabelsi created</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:36:14</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>TRX-100057</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Transfer 91000020 → 91000021</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:36:57</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>TRX-100058</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Transfer 91000020 → 91000021</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:38:58</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>0</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Customer Amine Ben Salah created</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:39:05</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>91000002</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>91000002</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>0</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Sousse</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Customer Sara Trabelsi created</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:39:11</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>91000003</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>91000003</t>
+        </is>
+      </c>
+      <c r="F138" t="n">
+        <v>0</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Customer Karim Mokhtar created</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-07-14 17:39:25</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="F139" t="n">
+        <v>0</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Customer Amine Ben Salah created</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-07-16 11:37:39</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="F140" t="n">
+        <v>0</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Customer Amine Ben Salah created</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-07-16 11:37:46</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>91000002</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>91000002</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>0</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Sousse</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Customer Sara Trabelsi created</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-07-16 11:39:24</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>TRX-100059</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>91000009</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>91000010</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>100</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Transfer 91000009 → 91000010</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-07-16 11:39:57</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>TRX-100060</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Transfer 91000020 → 91000021</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-07-16 12:24:07</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="F144" t="n">
+        <v>0</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Customer Amine Ben Salah created</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-07-16 12:24:13</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>91000002</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>91000002</t>
+        </is>
+      </c>
+      <c r="F145" t="n">
+        <v>0</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Sousse</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Customer Sara Trabelsi created</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-07-16 12:25:05</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>TRX-100061</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>91000009</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>91000010</t>
+        </is>
+      </c>
+      <c r="F146" t="n">
+        <v>100</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Transfer 91000009 → 91000010</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-07-16 12:25:36</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>TRX-100062</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="F147" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Transfer 91000020 → 91000021</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-07-16 12:28:55</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="F148" t="n">
+        <v>0</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Customer Amine Ben Salah created</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-07-16 12:29:06</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="F149" t="n">
+        <v>0</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Customer Amine Ben Salah created</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-07-16 12:29:11</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>91000002</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>91000002</t>
+        </is>
+      </c>
+      <c r="F150" t="n">
+        <v>0</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Sousse</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Customer Sara Trabelsi created</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-07-16 12:29:16</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>91000003</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>91000003</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>0</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Customer Karim Mokhtar created</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-07-16 12:35:53</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="F152" t="n">
+        <v>0</v>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Customer Amine Ben Salah created</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-07-16 12:35:59</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>91000002</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>91000002</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>0</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Sousse</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Customer Sara Trabelsi created</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-07-16 12:36:54</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>91000001</t>
+        </is>
+      </c>
+      <c r="F154" t="n">
+        <v>0</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Customer Amine Ben Salah created</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-07-16 12:36:59</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>91000002</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>91000002</t>
+        </is>
+      </c>
+      <c r="F155" t="n">
+        <v>0</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Sousse</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Customer Sara Trabelsi created</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-07-16 12:37:04</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>91000003</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>91000003</t>
+        </is>
+      </c>
+      <c r="F156" t="n">
+        <v>0</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Customer Karim Mokhtar created</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-07-16 12:37:47</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>TRX-100063</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>91000009</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>91000010</t>
+        </is>
+      </c>
+      <c r="F157" t="n">
+        <v>100</v>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Transfer 91000009 → 91000010</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-07-16 12:38:19</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>TRX-100064</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="F158" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Transfer 91000020 → 91000021</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-07-16 12:48:20</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>12345645</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>12345645</t>
+        </is>
+      </c>
+      <c r="F159" t="n">
+        <v>0</v>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Customer neyrouz created</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-07-16 12:48:25</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>91000002</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>91000002</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
+        <v>0</v>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Sousse</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Customer Test Customer 2 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-07-16 12:48:30</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>91000003</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>91000003</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
+        <v>0</v>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Customer Test Customer 3 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-07-16 12:49:13</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>TRX-100065</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>91000009</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>91000010</t>
+        </is>
+      </c>
+      <c r="F162" t="n">
+        <v>100</v>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Transfer 91000009 → 91000010</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-07-16 12:49:45</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>TRX-100066</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="F163" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Transfer 91000020 → 91000021</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-07-16 13:05:31</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>12345645</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>12345645</t>
+        </is>
+      </c>
+      <c r="F164" t="n">
+        <v>0</v>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Customer neyrouz t created</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-07-16 13:05:36</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>22222222</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>22222222</t>
+        </is>
+      </c>
+      <c r="F165" t="n">
+        <v>0</v>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Customer maryem created</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-07-16 13:05:41</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>33333333</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>33333333</t>
+        </is>
+      </c>
+      <c r="F166" t="n">
+        <v>0</v>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Customer salem created</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-07-16 13:06:24</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>TRX-100067</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>11111111</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>22223333</t>
+        </is>
+      </c>
+      <c r="F167" t="n">
+        <v>100</v>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Transfer 11111111 → 22223333</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-07-16 13:06:55</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>TRX-100068</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="F168" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Transfer 91000020 → 91000021</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-07-16 13:08:20</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>12345689</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>12345689</t>
+        </is>
+      </c>
+      <c r="F169" t="n">
+        <v>0</v>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Tunis</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Customer amina created</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-07-16 13:13:47</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>12345645</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>12345645</t>
+        </is>
+      </c>
+      <c r="F170" t="n">
+        <v>0</v>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Customer neyrouz t created</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-07-16 13:13:52</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>22222222</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>22222222</t>
+        </is>
+      </c>
+      <c r="F171" t="n">
+        <v>0</v>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Customer maryem created</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-07-16 13:13:57</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>33333333</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>33333333</t>
+        </is>
+      </c>
+      <c r="F172" t="n">
+        <v>0</v>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Customer salem created</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-07-16 13:14:40</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>TRX-100069</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>11111111</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>22223333</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
+        <v>100</v>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Transfer 11111111 → 22223333</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-07-16 13:15:12</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>TRX-100070</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="F174" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Transfer 91000020 → 91000021</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-07-16 15:07:48</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>12345645</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>12345645</t>
+        </is>
+      </c>
+      <c r="F175" t="n">
+        <v>0</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Customer neyrouz t created</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-07-16 15:07:58</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>22222222</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>22222222</t>
+        </is>
+      </c>
+      <c r="F176" t="n">
+        <v>0</v>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Customer maryem created</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-07-16 15:08:11</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>33333333</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>33333333</t>
+        </is>
+      </c>
+      <c r="F177" t="n">
+        <v>0</v>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Customer salem created</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-07-16 15:09:17</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>TRX-100071</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>11111111</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>22223333</t>
+        </is>
+      </c>
+      <c r="F178" t="n">
+        <v>100</v>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Transfer 11111111 → 22223333</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-07-16 15:09:59</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>TRX-100072</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>91000020</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="F179" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>ATM</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Transfer 91000020 → 91000021</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-07-16 15:10:26</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>45678945</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>45678945</t>
+        </is>
+      </c>
+      <c r="F180" t="n">
+        <v>0</v>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Sfax</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Customer jamel created</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-07-16 15:12:54</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>78945678</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>78945678</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
+        <v>0</v>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Customer user 10 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-07-16 15:14:25</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>22222222</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>22222222</t>
+        </is>
+      </c>
+      <c r="F182" t="n">
+        <v>0</v>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Customer maryem created</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-07-16 15:18:01</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>78945678</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>78945678</t>
+        </is>
+      </c>
+      <c r="F183" t="n">
+        <v>0</v>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Customer user 10 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-07-16 15:18:07</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>12345645</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>12345645</t>
+        </is>
+      </c>
+      <c r="F184" t="n">
+        <v>0</v>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Customer neyrouz t created</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-07-16 15:18:11</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>22222222</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>22222222</t>
+        </is>
+      </c>
+      <c r="F185" t="n">
+        <v>0</v>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Customer maryem created</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-07-16 15:33:04</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>78945678</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>78945678</t>
+        </is>
+      </c>
+      <c r="F186" t="n">
+        <v>0</v>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Customer user 10 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-07-16 15:33:10</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>12345645</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>12345645</t>
+        </is>
+      </c>
+      <c r="F187" t="n">
+        <v>0</v>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Customer neyrouz t created</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-07-16 15:33:15</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>22222222</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>22222222</t>
+        </is>
+      </c>
+      <c r="F188" t="n">
+        <v>0</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Customer maryem created</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-07-16 15:34:01</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>TRX-100073</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>99999999</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>11111111</t>
+        </is>
+      </c>
+      <c r="F189" t="n">
+        <v>100</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Sousse</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Transfer 99999999 → 11111111</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/activity.xlsx
+++ b/data/activity.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K189"/>
+  <dimension ref="A1:K198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10238,6 +10238,476 @@
         </is>
       </c>
     </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-07-16 15:43:19</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>78945678</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>78945678</t>
+        </is>
+      </c>
+      <c r="F190" t="n">
+        <v>0</v>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Customer user 10 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-07-16 15:43:24</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>12345645</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>12345645</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>0</v>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Customer neyrouz t created</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-07-16 15:43:29</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>22222222</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>22222222</t>
+        </is>
+      </c>
+      <c r="F192" t="n">
+        <v>0</v>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Customer maryem created</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-07-16 15:44:26</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>TRX-100074</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>99999999</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>11111111</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>100</v>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Sousse</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Transfer 99999999 → 11111111</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-07-16 15:44:58</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>TRX-100075</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>77779999</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="F194" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Transfer 77779999 → 91000021</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-07-16 15:54:41</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>78945678</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>78945678</t>
+        </is>
+      </c>
+      <c r="F195" t="n">
+        <v>0</v>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Customer user 10 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-07-16 15:56:13</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>78945678</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>78945678</t>
+        </is>
+      </c>
+      <c r="F196" t="n">
+        <v>0</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Customer user 1 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-07-16 15:59:34</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>TRX-100076</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>77779999</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="F197" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Transfer 77779999 → 91000021</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-07-16 15:59:44</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>TRX-100077</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>77779999</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="F198" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Transfer 77779999 → 91000021</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/activity.xlsx
+++ b/data/activity.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K198"/>
+  <dimension ref="A1:K242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10708,6 +10708,2251 @@
         </is>
       </c>
     </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-07-16 16:18:46</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>91000101</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>91000101</t>
+        </is>
+      </c>
+      <c r="F199" t="n">
+        <v>0</v>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Tunis</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Customer Test Customer 101 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-07-16 16:19:53</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>91000101</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>91000101</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
+        <v>0</v>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Tunis</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Customer Test Customer 101 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-07-16 16:20:51</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>91000101</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>91000101</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>0</v>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Tunis</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Customer Test Customer 101 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-07-16 16:27:32</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>91000101</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>91000101</t>
+        </is>
+      </c>
+      <c r="F202" t="n">
+        <v>0</v>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Tunis</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Customer Test Customer 101 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-07-16 16:31:14</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>91000101</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>91000101</t>
+        </is>
+      </c>
+      <c r="F203" t="n">
+        <v>0</v>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Tunis</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Customer Test Customer 101 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-07-16 16:46:45</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>91000101</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>91000101</t>
+        </is>
+      </c>
+      <c r="F204" t="n">
+        <v>0</v>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Tunis</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Customer Test Customer 101 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-07-16 16:56:09</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>78945678</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>78945678</t>
+        </is>
+      </c>
+      <c r="F205" t="n">
+        <v>0</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Customer user 10 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-07-16 16:56:16</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>78945678</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>78945678</t>
+        </is>
+      </c>
+      <c r="F206" t="n">
+        <v>0</v>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Customer user 10 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-07-16 16:56:32</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>12345645</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>12345645</t>
+        </is>
+      </c>
+      <c r="F207" t="n">
+        <v>0</v>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Customer neyrouz t created</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-07-16 16:56:39</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>22222222</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>22222222</t>
+        </is>
+      </c>
+      <c r="F208" t="n">
+        <v>0</v>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Customer maryem created</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-07-16 16:57:21</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>91000101</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>91000101</t>
+        </is>
+      </c>
+      <c r="F209" t="n">
+        <v>0</v>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Tunis</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Customer Test Customer 101 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-07-16 16:57:34</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>12345645</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>12345645</t>
+        </is>
+      </c>
+      <c r="F210" t="n">
+        <v>0</v>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Customer neyrouz t created</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-07-16 16:58:59</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>22222222</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>22222222</t>
+        </is>
+      </c>
+      <c r="F211" t="n">
+        <v>0</v>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Customer maryem created</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-07-16 17:04:52</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>TRX-100078</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>99999999</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>11111111</t>
+        </is>
+      </c>
+      <c r="F212" t="n">
+        <v>100</v>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Sousse</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Transfer 99999999 → 11111111</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-07-16 17:06:28</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>TRX-100079</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>77779999</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="F213" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Transfer 77779999 → 91000021</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-07-16 17:41:15</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>78945678</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>78945678</t>
+        </is>
+      </c>
+      <c r="F214" t="n">
+        <v>0</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Customer user 10 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-07-16 17:41:21</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>12345645</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>12345645</t>
+        </is>
+      </c>
+      <c r="F215" t="n">
+        <v>0</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Customer neyrouz t created</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-07-16 17:41:27</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>22222222</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>22222222</t>
+        </is>
+      </c>
+      <c r="F216" t="n">
+        <v>0</v>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Customer maryem created</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-07-16 17:41:56</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>91000101</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>91000101</t>
+        </is>
+      </c>
+      <c r="F217" t="n">
+        <v>0</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Tunis</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Customer Test Customer 101 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-07-16 17:43:01</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>91000102</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>91000102</t>
+        </is>
+      </c>
+      <c r="F218" t="n">
+        <v>0</v>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Tunis</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Customer Test Customer 102 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-07-16 17:44:37</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>TRX-100080</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>99999999</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>11111111</t>
+        </is>
+      </c>
+      <c r="F219" t="n">
+        <v>100</v>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Sousse</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Transfer 99999999 → 11111111</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-07-16 17:46:08</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>TRX-100081</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>77779999</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="F220" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Transfer 77779999 → 91000021</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-07-16 17:55:04</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>91000101</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>91000101</t>
+        </is>
+      </c>
+      <c r="F221" t="n">
+        <v>0</v>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Tunis</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Customer Test Customer 101 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-07-16 17:56:00</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>91000102</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>91000102</t>
+        </is>
+      </c>
+      <c r="F222" t="n">
+        <v>0</v>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Tunis</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Customer Test Customer 102 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-07-16 17:56:48</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>14725836</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>14725836</t>
+        </is>
+      </c>
+      <c r="F223" t="n">
+        <v>0</v>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Customer salima created</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-07-16 17:58:14</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>91000101</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>91000101</t>
+        </is>
+      </c>
+      <c r="F224" t="n">
+        <v>0</v>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Tunis</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Customer Test Customer 101 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:49:36</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>91000101</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>91000101</t>
+        </is>
+      </c>
+      <c r="F225" t="n">
+        <v>0</v>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Tunis</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Customer Test Customer 101 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:51:11</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>91000101</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>91000101</t>
+        </is>
+      </c>
+      <c r="F226" t="n">
+        <v>0</v>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Tunis</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Customer Test Customer 101 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:51:59</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>78945678</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>78945678</t>
+        </is>
+      </c>
+      <c r="F227" t="n">
+        <v>0</v>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Customer user 10 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:52:04</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>12345645</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>12345645</t>
+        </is>
+      </c>
+      <c r="F228" t="n">
+        <v>0</v>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Customer neyrouz t created</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:52:09</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>22222222</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>22222222</t>
+        </is>
+      </c>
+      <c r="F229" t="n">
+        <v>0</v>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Customer maryem created</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:52:37</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>91000101</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>91000101</t>
+        </is>
+      </c>
+      <c r="F230" t="n">
+        <v>0</v>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Tunis</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Customer Test Customer 101 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:53:38</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>91000102</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>91000102</t>
+        </is>
+      </c>
+      <c r="F231" t="n">
+        <v>0</v>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Tunis</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Customer Test Customer 102 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:54:50</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>TRX-100082</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>99999999</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>11111111</t>
+        </is>
+      </c>
+      <c r="F232" t="n">
+        <v>100</v>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Sousse</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Transfer 99999999 → 11111111</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:55:25</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>TRX-100083</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>77779999</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>91000021</t>
+        </is>
+      </c>
+      <c r="F233" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Mobile App</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Transfer 77779999 → 91000021</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-07-28 00:09:35</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>12312312</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>12312312</t>
+        </is>
+      </c>
+      <c r="F234" t="n">
+        <v>0</v>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Sousse</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Customer sirine created</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-07-28 00:09:55</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>InsuranceSubscription</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Hospitalière/Pack 1</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>12312312</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>12312312</t>
+        </is>
+      </c>
+      <c r="F235" t="n">
+        <v>200</v>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Sousse</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Insurance Hospitalière - Pack 1 (200.0€) for sirine</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-07-28 00:10:33</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>78945678</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>78945678</t>
+        </is>
+      </c>
+      <c r="F236" t="n">
+        <v>0</v>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Customer user 10 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-07-28 00:10:37</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>12345645</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>12345645</t>
+        </is>
+      </c>
+      <c r="F237" t="n">
+        <v>0</v>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Customer neyrouz t created</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-07-28 00:10:42</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>22222222</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>22222222</t>
+        </is>
+      </c>
+      <c r="F238" t="n">
+        <v>0</v>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Customer maryem created</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-07-28 00:11:09</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>91000101</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>91000101</t>
+        </is>
+      </c>
+      <c r="F239" t="n">
+        <v>0</v>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Tunis</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Customer Test Customer 101 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-07-28 00:12:08</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>CustomerCreated</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>91000102</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>91000102</t>
+        </is>
+      </c>
+      <c r="F240" t="n">
+        <v>0</v>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Tunis</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Desktop App</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Customer Test Customer 102 created</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-07-28 00:13:16</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>TRX-100084</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>99999999</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>11111111</t>
+        </is>
+      </c>
+      <c r="F241" t="n">
+        <v>100</v>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Sousse</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Transfer 99999999 → 11111111</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-07-28 00:13:47</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Transfer</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>TRX-100085</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>77779999</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>12312312</t>
+        </is>
+      </c>
+      <c r="F242" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>Success</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Web Banking</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Transfer 77779999 → 12312312</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
